--- a/data/trans_orig/IP07C20-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C20-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>28265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76042</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>41950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>31873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50037</t>
+          <t>48432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39409</t>
+          <t>39826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71089</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92465</t>
+          <t>92248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35305</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>40078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>49316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70279</t>
+          <t>69433</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>34871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>26591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39587</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49679</t>
+          <t>50111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29674</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>44654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43791</t>
+          <t>42913</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61887</t>
+          <t>61283</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83647</t>
+          <t>83229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30712</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>33308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52157</t>
+          <t>51017</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52546</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>75725</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92690</t>
+          <t>92827</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127934</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160549</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146235</t>
+          <t>147012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>112363</t>
+          <t>111760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>139751</t>
+          <t>140026</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>237900</t>
+          <t>240181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>278224</t>
+          <t>278679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>66036</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>90556</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>77127</t>
+          <t>76117</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103249</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>147749</t>
+          <t>149753</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>184743</t>
+          <t>185089</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32312</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>29877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57549</t>
+          <t>56912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>44048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61188</t>
+          <t>62664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,47 +4876,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3782</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8136</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3782</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8706</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26811</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>24031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>38979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54830</t>
+          <t>55311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75685</t>
+          <t>76318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44495</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29127</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62591</t>
+          <t>63291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83568</t>
+          <t>83839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>56166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>29953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>39424</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46055</t>
+          <t>46821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64892</t>
+          <t>64505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23360</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39204</t>
+          <t>38724</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>48233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69235</t>
+          <t>69541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37805</t>
+          <t>37865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44322</t>
+          <t>44962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>55943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77506</t>
+          <t>77499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28180</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>100830</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128582</t>
+          <t>129665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98207</t>
+          <t>96875</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>125520</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>207350</t>
+          <t>208182</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>247499</t>
+          <t>247271</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97198</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125743</t>
+          <t>124808</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>130872</t>
+          <t>130403</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>206826</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>247382</t>
+          <t>245751</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58621</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58223</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82630</t>
+          <t>82342</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>122312</t>
+          <t>123759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156617</t>
+          <t>156875</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>20537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44636</t>
+          <t>45328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>29811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36525</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55983</t>
+          <t>56493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26840</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28579</t>
+          <t>28958</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54247</t>
+          <t>53364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47638</t>
+          <t>47946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51467</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71124</t>
+          <t>71876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94189</t>
+          <t>93361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43756</t>
+          <t>43380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>55087</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76703</t>
+          <t>76977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>28890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56488</t>
+          <t>57329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22246</t>
+          <t>21759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52440</t>
+          <t>52300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>26142</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>31590</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49723</t>
+          <t>48454</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>41079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41680</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61892</t>
+          <t>62607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48036</t>
+          <t>47972</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60240</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83191</t>
+          <t>83255</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>34340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43347</t>
+          <t>43396</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64800</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>26822</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>77235</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>103648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74724</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>102420</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>161167</t>
+          <t>159706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>198240</t>
+          <t>198572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>95880</t>
+          <t>96745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>126221</t>
+          <t>124864</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115819</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>146837</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220606</t>
+          <t>220546</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>261094</t>
+          <t>261124</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85981</t>
+          <t>87073</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114152</t>
+          <t>115098</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84717</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112882</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>178407</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>215090</t>
+          <t>217021</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>32753</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66899</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
